--- a/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
+++ b/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41C32E4F-D2D6-49D7-ABDA-518F29E1BF99}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{760206F9-39D2-4B33-B380-01871B3B3ABE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="656">
   <si>
     <t>end location</t>
   </si>
@@ -1985,6 +1985,9 @@
   </si>
   <si>
     <t>energy consuMption</t>
+  </si>
+  <si>
+    <t>06::00</t>
   </si>
 </sst>
 </file>
@@ -2465,7 +2468,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>655</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>

--- a/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
+++ b/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{760206F9-39D2-4B33-B380-01871B3B3ABE}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06102D57-1312-49A7-92B6-1C406DFCFEEC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="657">
   <si>
     <t>end location</t>
   </si>
@@ -1978,16 +1978,19 @@
     <t>14:50:00</t>
   </si>
   <si>
-    <t>Start location</t>
-  </si>
-  <si>
-    <t>l_ine</t>
-  </si>
-  <si>
-    <t>energy consuMption</t>
-  </si>
-  <si>
     <t>06::00</t>
+  </si>
+  <si>
+    <t>start location</t>
+  </si>
+  <si>
+    <t>start time</t>
+  </si>
+  <si>
+    <t>line</t>
+  </si>
+  <si>
+    <t>energy consumption</t>
   </si>
 </sst>
 </file>
@@ -2363,12 +2366,14 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2376,10 +2381,10 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -2468,7 +2473,7 @@
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>

--- a/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
+++ b/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0B86E46-4C92-43DF-8F5F-C299C4B5EF9F}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A795DA5A-E463-4506-989E-3873B57C419C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3607" uniqueCount="656">
   <si>
     <t>end location</t>
   </si>
@@ -1973,9 +1973,6 @@
   </si>
   <si>
     <t>14:50:00</t>
-  </si>
-  <si>
-    <t>06::00</t>
   </si>
   <si>
     <t>start location</t>
@@ -2047,11 +2044,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2366,13 +2364,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -2381,13 +2379,13 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2472,8 +2470,8 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
-        <v>651</v>
+      <c r="D5" s="2">
+        <v>0.27013888888888887</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>

--- a/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
+++ b/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A795DA5A-E463-4506-989E-3873B57C419C}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3B32AA-3CF9-43CE-BBA4-D30263E5FBBC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
+++ b/Streamlit/Bus_Plan_Cleaned_kopie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Project/Project_5/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB3B32AA-3CF9-43CE-BBA4-D30263E5FBBC}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_07FD1DEB156FFE0F62355476585DCE3A87430DBE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DA4F0EB-8C16-4963-A79E-A58E9E4545DB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1981,13 +1981,13 @@
     <t>start time</t>
   </si>
   <si>
-    <t>line</t>
-  </si>
-  <si>
     <t>energy consumption</t>
   </si>
   <si>
     <t>Bus</t>
+  </si>
+  <si>
+    <t>06::00</t>
   </si>
 </sst>
 </file>
@@ -2378,14 +2378,12 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>654</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2470,8 +2468,8 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="2">
-        <v>0.27013888888888887</v>
+      <c r="D5" s="2" t="s">
+        <v>655</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
